--- a/news_daily/2026-10-07.xlsx
+++ b/news_daily/2026-10-07.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -58,11 +58,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF9C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -93,9 +88,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -463,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BL18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +518,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +823,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -1011,6 +1027,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1189,6 +1209,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1367,6 +1391,10 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1545,6 +1573,10 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1723,6 +1755,10 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1893,6 +1929,10 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2071,6 +2111,10 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2249,6 +2293,10 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2419,6 +2467,10 @@
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2597,6 +2649,10 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2751,6 +2807,10 @@
       <c r="BF12" s="2" t="inlineStr"/>
       <c r="BG12" s="2" t="inlineStr"/>
       <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2929,6 +2989,10 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr"/>
+      <c r="BL13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3099,184 +3163,216 @@
         </is>
       </c>
       <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr"/>
+      <c r="BL14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>EFX</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Equifax, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-10-07T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>What to do if you qualify for the Equifax error settlement</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>'-0.089</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQY1NfU2k3QmpsaTJJendiLXpGWFNpWEJBVkJfMnZ5aV9ROEhOLUJ0NEJoblVIbnZnOVpNazZkQlRvMTZJRExJZHU1M2w3QmEyY0c1WnRFUjliUW9iM2M0V0c5TV9ZNnNQVi1TcUFfd1Y0ZzF1RExYV2g1ak1tZGNPTVlBekdteG5mSll0dGppNNIBlAFBVV95cUxPS2dRT1c0bXFVX0tzMmhvZV8yb0VKbUVpUXRMSXM4YUNLYVptdWMwcnYtRkc5UjJSVU9WdVl5Zm5ZM3N5dXJrYmdGR2RaYUVBQzJNSUxZekRwQldkOXExdGVGcWxHb2VSZ2RueWtHMUxFbnJ4QjZfY3ZSelpSNXdSX0tYRUhLdV9FVEdjZl9OVlVqejVs?oc=5</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>NewsNation</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>52f9204ecb3943549531b3b7e657269f</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>5a9ed5f0ead96a509305f4f7</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>a9532f6c9ffdf4af6bef1d1d</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>EFX-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AK15" s="2" t="inlineStr"/>
+      <c r="AL15" s="2" t="inlineStr"/>
+      <c r="AM15" s="2" t="inlineStr"/>
+      <c r="AN15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>'-0.089</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQY1NfU2k3QmpsaTJJendiLXpGWFNpWEJBVkJfMnZ5aV9ROEhOLUJ0NEJoblVIbnZnOVpNazZkQlRvMTZJRExJZHU1M2w3QmEyY0c1WnRFUjliUW9iM2M0V0c5TV9ZNnNQVi1TcUFfd1Y0ZzF1RExYV2g1ak1tZGNPTVlBekdteG5mSll0dGppNNIBlAFBVV95cUxPS2dRT1c0bXFVX0tzMmhvZV8yb0VKbUVpUXRMSXM4YUNLYVptdWMwcnYtRkc5UjJSVU9WdVl5Zm5ZM3N5dXJrYmdGR2RaYUVBQzJNSUxZekRwQldkOXExdGVGcWxHb2VSZ2RueWtHMUxFbnJ4QjZfY3ZSelpSNXdSX0tYRUhLdV9FVEdjZl9OVlVqejVs?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>NewsNation</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z15" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA15" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="inlineStr">
-        <is>
-          <t>5a9ed5f0ead96a509305f4f7</t>
-        </is>
-      </c>
-      <c r="AD15" s="4" t="inlineStr">
-        <is>
-          <t>a9532f6c9ffdf4af6bef1d1d</t>
-        </is>
-      </c>
-      <c r="AE15" s="4" t="inlineStr">
-        <is>
-          <t>EFX-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF15" s="4" t="inlineStr"/>
-      <c r="AG15" s="4" t="inlineStr"/>
-      <c r="AH15" s="4" t="inlineStr"/>
-      <c r="AI15" s="4" t="inlineStr"/>
-      <c r="AJ15" s="4" t="inlineStr"/>
-      <c r="AK15" s="4" t="inlineStr"/>
-      <c r="AL15" s="4" t="inlineStr"/>
-      <c r="AM15" s="4" t="inlineStr"/>
-      <c r="AN15" s="4" t="inlineStr"/>
-      <c r="AO15" s="4" t="inlineStr"/>
-      <c r="AP15" s="4" t="inlineStr"/>
-      <c r="AQ15" s="4" t="inlineStr"/>
-      <c r="AR15" s="4" t="inlineStr"/>
-      <c r="AS15" s="4" t="inlineStr"/>
-      <c r="AT15" s="4" t="inlineStr"/>
-      <c r="AU15" s="4" t="inlineStr"/>
-      <c r="AV15" s="4" t="inlineStr"/>
-      <c r="AW15" s="4" t="inlineStr">
+      <c r="AP15" s="2" t="inlineStr"/>
+      <c r="AQ15" s="2" t="inlineStr"/>
+      <c r="AR15" s="2" t="inlineStr"/>
+      <c r="AS15" s="2" t="inlineStr"/>
+      <c r="AT15" s="2" t="inlineStr"/>
+      <c r="AU15" s="2" t="inlineStr"/>
+      <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX15" s="4" t="inlineStr"/>
-      <c r="AY15" s="4" t="inlineStr"/>
-      <c r="AZ15" s="4" t="inlineStr"/>
-      <c r="BA15" s="4" t="inlineStr"/>
-      <c r="BB15" s="4" t="inlineStr">
+      <c r="AX15" s="2" t="inlineStr"/>
+      <c r="AY15" s="2" t="inlineStr"/>
+      <c r="AZ15" s="2" t="inlineStr"/>
+      <c r="BA15" s="2" t="inlineStr"/>
+      <c r="BB15" s="2" t="inlineStr">
         <is>
           <t>EFX</t>
         </is>
       </c>
-      <c r="BC15" s="4" t="inlineStr">
+      <c r="BC15" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD15" s="4" t="inlineStr"/>
-      <c r="BE15" s="4" t="inlineStr">
+      <c r="BD15" s="2" t="inlineStr"/>
+      <c r="BE15" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF15" s="4" t="inlineStr">
+      <c r="BF15" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG15" s="4" t="inlineStr">
+      <c r="BG15" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH15" s="4" t="inlineStr"/>
+      <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3447,6 +3543,10 @@
       <c r="BF16" s="2" t="inlineStr"/>
       <c r="BG16" s="2" t="inlineStr"/>
       <c r="BH16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr"/>
+      <c r="BL16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3625,187 +3725,219 @@
         </is>
       </c>
       <c r="BH17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BJ17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr"/>
+      <c r="BL17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>EFX</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Equifax, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>2026-10-07T00:12:00+08:00</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Eligible for a payout? Some Equifax customers could get up to $280 in $100 million settlement</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.655</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNVi1KMVVBN0h3bWNsS2RSVy1zaGtVMWNRV29NRWNxZ3BkMmwwaXUzdmdjTHZFVGs0dHBTeTBmYTFCN3BoVDZGaS00Tno2Zjk0ZFVsZndlX2xBMU1UNkRJOWZQVU9ESTF4dnE1OWJLVFJ4eW9sQTFOUko4VmU5LUotb3RXYVBoaVhGQ05vVEJpam9SY2FwSldBSnU0U042UTFoVjFIU29UVTI2NXNnYmRVNXoxa3FZUm5OWlU0VdIB0AFBVV95cUxQRFJLSVR1dTh5NWc5M3p4UVh5UmM2b3lzMHRXaDI2OGFacWtIckp6V1R2SGtiOGRuUXRsWTZfaUtyY2ItR01WVXpaWjB0MUFHRkxHSTdVb3pPWjllYXdnb08wbUtRcVJHajFWQnBuU1VteVR2cGNlWFVwNnNMbnVPTVBsclQ2T2dsbF90UzVlUTQyX1dhamVHcmVYcUppU01KeEJ0Zm9xdm1sMWlyYmFtNWplNDE4S0JmQ0J4dkhZU3lnZndERWxGVmQxdFNqUk9Q?oc=5</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Dakota News Now</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>e2b3ab67a7dc4cde992135c2776d8dba</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>399b8565a2c91ea03fd1a6bd</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>541ad40363f83dcc691173db</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
+          <t>EFX-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+      <c r="AK18" s="2" t="inlineStr"/>
+      <c r="AL18" s="2" t="inlineStr"/>
+      <c r="AM18" s="2" t="inlineStr"/>
+      <c r="AN18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>0.655</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNVi1KMVVBN0h3bWNsS2RSVy1zaGtVMWNRV29NRWNxZ3BkMmwwaXUzdmdjTHZFVGs0dHBTeTBmYTFCN3BoVDZGaS00Tno2Zjk0ZFVsZndlX2xBMU1UNkRJOWZQVU9ESTF4dnE1OWJLVFJ4eW9sQTFOUko4VmU5LUotb3RXYVBoaVhGQ05vVEJpam9SY2FwSldBSnU0U042UTFoVjFIU29UVTI2NXNnYmRVNXoxa3FZUm5OWlU0VdIB0AFBVV95cUxQRFJLSVR1dTh5NWc5M3p4UVh5UmM2b3lzMHRXaDI2OGFacWtIckp6V1R2SGtiOGRuUXRsWTZfaUtyY2ItR01WVXpaWjB0MUFHRkxHSTdVb3pPWjllYXdnb08wbUtRcVJHajFWQnBuU1VteVR2cGNlWFVwNnNMbnVPTVBsclQ2T2dsbF90UzVlUTQyX1dhamVHcmVYcUppU01KeEJ0Zm9xdm1sMWlyYmFtNWplNDE4S0JmQ0J4dkhZU3lnZndERWxGVmQxdFNqUk9Q?oc=5</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>Dakota News Now</t>
-        </is>
-      </c>
-      <c r="W18" s="4" t="inlineStr"/>
-      <c r="X18" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y18" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z18" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA18" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="4" t="inlineStr"/>
-      <c r="AC18" s="4" t="inlineStr">
-        <is>
-          <t>399b8565a2c91ea03fd1a6bd</t>
-        </is>
-      </c>
-      <c r="AD18" s="4" t="inlineStr">
-        <is>
-          <t>541ad40363f83dcc691173db</t>
-        </is>
-      </c>
-      <c r="AE18" s="4" t="inlineStr">
-        <is>
-          <t>EFX-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF18" s="4" t="inlineStr"/>
-      <c r="AG18" s="4" t="inlineStr"/>
-      <c r="AH18" s="4" t="inlineStr"/>
-      <c r="AI18" s="4" t="inlineStr"/>
-      <c r="AJ18" s="4" t="inlineStr"/>
-      <c r="AK18" s="4" t="inlineStr"/>
-      <c r="AL18" s="4" t="inlineStr"/>
-      <c r="AM18" s="4" t="inlineStr"/>
-      <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr"/>
-      <c r="AP18" s="4" t="inlineStr"/>
-      <c r="AQ18" s="4" t="inlineStr"/>
-      <c r="AR18" s="4" t="inlineStr"/>
-      <c r="AS18" s="4" t="inlineStr"/>
-      <c r="AT18" s="4" t="inlineStr"/>
-      <c r="AU18" s="4" t="inlineStr"/>
-      <c r="AV18" s="4" t="inlineStr"/>
-      <c r="AW18" s="4" t="inlineStr">
+      <c r="AP18" s="2" t="inlineStr"/>
+      <c r="AQ18" s="2" t="inlineStr"/>
+      <c r="AR18" s="2" t="inlineStr"/>
+      <c r="AS18" s="2" t="inlineStr"/>
+      <c r="AT18" s="2" t="inlineStr"/>
+      <c r="AU18" s="2" t="inlineStr"/>
+      <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX18" s="4" t="inlineStr"/>
-      <c r="AY18" s="4" t="inlineStr"/>
-      <c r="AZ18" s="4" t="inlineStr"/>
-      <c r="BA18" s="4" t="inlineStr"/>
-      <c r="BB18" s="4" t="inlineStr">
+      <c r="AX18" s="2" t="inlineStr"/>
+      <c r="AY18" s="2" t="inlineStr"/>
+      <c r="AZ18" s="2" t="inlineStr"/>
+      <c r="BA18" s="2" t="inlineStr"/>
+      <c r="BB18" s="2" t="inlineStr">
         <is>
           <t>EFX</t>
         </is>
       </c>
-      <c r="BC18" s="4" t="inlineStr">
+      <c r="BC18" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD18" s="4" t="inlineStr"/>
-      <c r="BE18" s="4" t="inlineStr">
+      <c r="BD18" s="2" t="inlineStr"/>
+      <c r="BE18" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF18" s="4" t="inlineStr">
+      <c r="BF18" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG18" s="4" t="inlineStr">
+      <c r="BG18" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH18" s="4" t="inlineStr"/>
+      <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH18"/>
+  <autoFilter ref="A1:BL18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3816,7 +3948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3879,6 +4011,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4180,6 +4316,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -4360,6 +4516,10 @@
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr"/>
+      <c r="BL2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -4530,6 +4690,10 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -4708,6 +4872,10 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -4878,365 +5046,13 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Equifax, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-07T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>What to do if you qualify for the Equifax error settlement</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>'-0.089</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQY1NfU2k3QmpsaTJJendiLXpGWFNpWEJBVkJfMnZ5aV9ROEhOLUJ0NEJoblVIbnZnOVpNazZkQlRvMTZJRExJZHU1M2w3QmEyY0c1WnRFUjliUW9iM2M0V0c5TV9ZNnNQVi1TcUFfd1Y0ZzF1RExYV2g1ak1tZGNPTVlBekdteG5mSll0dGppNNIBlAFBVV95cUxPS2dRT1c0bXFVX0tzMmhvZV8yb0VKbUVpUXRMSXM4YUNLYVptdWMwcnYtRkc5UjJSVU9WdVl5Zm5ZM3N5dXJrYmdGR2RaYUVBQzJNSUxZekRwQldkOXExdGVGcWxHb2VSZ2RueWtHMUxFbnJ4QjZfY3ZSelpSNXdSX0tYRUhLdV9FVEdjZl9OVlVqejVs?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>NewsNation</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>5a9ed5f0ead96a509305f4f7</t>
-        </is>
-      </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>a9532f6c9ffdf4af6bef1d1d</t>
-        </is>
-      </c>
-      <c r="AE6" s="4" t="inlineStr">
-        <is>
-          <t>EFX-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="BC6" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Equifax, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-07T00:12:00+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Eligible for a payout? Some Equifax customers could get up to $280 in $100 million settlement</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>0.655</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNVi1KMVVBN0h3bWNsS2RSVy1zaGtVMWNRV29NRWNxZ3BkMmwwaXUzdmdjTHZFVGs0dHBTeTBmYTFCN3BoVDZGaS00Tno2Zjk0ZFVsZndlX2xBMU1UNkRJOWZQVU9ESTF4dnE1OWJLVFJ4eW9sQTFOUko4VmU5LUotb3RXYVBoaVhGQ05vVEJpam9SY2FwSldBSnU0U042UTFoVjFIU29UVTI2NXNnYmRVNXoxa3FZUm5OWlU0VdIB0AFBVV95cUxQRFJLSVR1dTh5NWc5M3p4UVh5UmM2b3lzMHRXaDI2OGFacWtIckp6V1R2SGtiOGRuUXRsWTZfaUtyY2ItR01WVXpaWjB0MUFHRkxHSTdVb3pPWjllYXdnb08wbUtRcVJHajFWQnBuU1VteVR2cGNlWFVwNnNMbnVPTVBsclQ2T2dsbF90UzVlUTQyX1dhamVHcmVYcUppU01KeEJ0Zm9xdm1sMWlyYmFtNWplNDE4S0JmQ0J4dkhZU3lnZndERWxGVmQxdFNqUk9Q?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>Dakota News Now</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z7" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="inlineStr">
-        <is>
-          <t>399b8565a2c91ea03fd1a6bd</t>
-        </is>
-      </c>
-      <c r="AD7" s="4" t="inlineStr">
-        <is>
-          <t>541ad40363f83dcc691173db</t>
-        </is>
-      </c>
-      <c r="AE7" s="4" t="inlineStr">
-        <is>
-          <t>EFX-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="4" t="inlineStr"/>
-      <c r="AZ7" s="4" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="BC7" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH7"/>
+  <autoFilter ref="A1:BL5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5247,7 +5063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH2"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5310,6 +5126,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5611,6 +5431,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -5783,9 +5623,13 @@
       <c r="BF2" s="2" t="inlineStr"/>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH2"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5796,7 +5640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5859,6 +5703,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6162,9 +6010,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6175,7 +6043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6225,134 +6093,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -6362,46 +6230,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6410,12 +6312,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -6425,90 +6327,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -6518,94 +6424,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -6613,89 +6519,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-10-07.xlsx
+++ b/news_daily/2026-10-07.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -1627,13 +1627,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1686,7 +1690,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>d8d93f4d6633427d8d394f612c100ecc</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>e3d0d32bcb3602e483465307</t>
@@ -1711,7 +1719,11 @@
       <c r="AL6" s="3" t="inlineStr"/>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="3" t="inlineStr"/>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
@@ -1757,8 +1769,16 @@
       <c r="BH6" s="3" t="inlineStr"/>
       <c r="BI6" s="3" t="inlineStr"/>
       <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1809,13 +1829,17 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1868,7 +1892,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>34ccc42edab04144b97f459c14484c13</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>f1a3f8687ded627c30122702</t>
@@ -1893,7 +1921,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -1931,8 +1963,16 @@
       <c r="BH7" s="3" t="inlineStr"/>
       <c r="BI7" s="3" t="inlineStr"/>
       <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2861,13 +2901,17 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -2920,7 +2964,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>6e255c9189054dec8657d4bc0ba2c3a2</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
           <t>f920a1fb349c77c3062ceb77</t>
@@ -2945,7 +2993,11 @@
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr"/>
       <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="3" t="inlineStr"/>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
@@ -2991,8 +3043,16 @@
       <c r="BH13" s="3" t="inlineStr"/>
       <c r="BI13" s="3" t="inlineStr"/>
       <c r="BJ13" s="3" t="inlineStr"/>
-      <c r="BK13" s="3" t="inlineStr"/>
-      <c r="BL13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3043,13 +3103,17 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -3102,7 +3166,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>6146264bf2c043f2aac26c520d2658bd</t>
+        </is>
+      </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
           <t>6194431dc700d25c69c7b888</t>
@@ -3127,7 +3195,11 @@
       <c r="AL14" s="3" t="inlineStr"/>
       <c r="AM14" s="3" t="inlineStr"/>
       <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="3" t="inlineStr"/>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr"/>
@@ -3165,8 +3237,16 @@
       <c r="BH14" s="3" t="inlineStr"/>
       <c r="BI14" s="3" t="inlineStr"/>
       <c r="BJ14" s="3" t="inlineStr"/>
-      <c r="BK14" s="3" t="inlineStr"/>
-      <c r="BL14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3385,7 +3465,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>AXP</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
           <t>American Express</t>
@@ -3419,17 +3503,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3482,7 +3566,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>baf0f3a5dd3449ccb1cbb0fd68182061</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>6e4a7b3d95209938c4973de3</t>
@@ -3509,7 +3597,7 @@
       <c r="AN16" s="2" t="inlineStr"/>
       <c r="AO16" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP16" s="2" t="inlineStr"/>
@@ -3543,10 +3631,22 @@
       <c r="BF16" s="2" t="inlineStr"/>
       <c r="BG16" s="2" t="inlineStr"/>
       <c r="BH16" s="2" t="inlineStr"/>
-      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr"/>
-      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4388,13 +4488,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -4447,7 +4551,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>d8d93f4d6633427d8d394f612c100ecc</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>e3d0d32bcb3602e483465307</t>
@@ -4472,7 +4580,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -4518,8 +4630,16 @@
       <c r="BH2" s="3" t="inlineStr"/>
       <c r="BI2" s="3" t="inlineStr"/>
       <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -4570,13 +4690,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -4629,7 +4753,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>34ccc42edab04144b97f459c14484c13</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>f1a3f8687ded627c30122702</t>
@@ -4654,7 +4782,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -4692,8 +4824,16 @@
       <c r="BH3" s="3" t="inlineStr"/>
       <c r="BI3" s="3" t="inlineStr"/>
       <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -4744,13 +4884,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -4803,7 +4947,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>6e255c9189054dec8657d4bc0ba2c3a2</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>f920a1fb349c77c3062ceb77</t>
@@ -4828,7 +4976,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -4874,8 +5026,16 @@
       <c r="BH4" s="3" t="inlineStr"/>
       <c r="BI4" s="3" t="inlineStr"/>
       <c r="BJ4" s="3" t="inlineStr"/>
-      <c r="BK4" s="3" t="inlineStr"/>
-      <c r="BL4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -4926,13 +5086,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -4985,7 +5149,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>6146264bf2c043f2aac26c520d2658bd</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>6194431dc700d25c69c7b888</t>
@@ -5010,7 +5178,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -5048,8 +5220,16 @@
       <c r="BH5" s="3" t="inlineStr"/>
       <c r="BI5" s="3" t="inlineStr"/>
       <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr"/>
-      <c r="BL5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL5"/>
@@ -5063,7 +5243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL2"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5454,182 +5634,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07T12:49:15+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>傑富瑞：將美國運通目標價下調至330美元</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>分析師降評</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0.083</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2699772</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>ANALYST_DOWNGRADE</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>目標價下調</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>6e4a7b3d95209938c4973de3</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>739f0c87f00118cb554c0ae7</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>AXP-ANALYST_DOWNGRADE-001</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>AXP</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>AXP</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr"/>
-      <c r="BF2" s="2" t="inlineStr"/>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL2"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-10-07.xlsx
+++ b/news_daily/2026-10-07.xlsx
@@ -880,28 +880,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -945,7 +949,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -958,7 +962,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>7c3b35f6743947ffa4414066c86949a1</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>b431f92d26b8eeacbb1d2883</t>
@@ -983,7 +991,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1027,10 +1039,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1081,13 +1105,17 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1140,7 +1168,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>91fafda2a3104571a7998d6b91ae5865</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>e4a1e4acb2fc863d37ef40a4</t>
@@ -1165,7 +1197,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1211,8 +1247,16 @@
       <c r="BH3" s="2" t="inlineStr"/>
       <c r="BI3" s="2" t="inlineStr"/>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1263,13 +1307,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1322,7 +1370,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>4b4c0d7808454698a7778e0803b0b79f</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>88a30d7972915e76d018c6da</t>
@@ -1347,7 +1399,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1393,8 +1449,16 @@
       <c r="BH4" s="2" t="inlineStr"/>
       <c r="BI4" s="2" t="inlineStr"/>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1430,28 +1494,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1491,7 +1559,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1504,7 +1572,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>c9c5168f909a4d148a038408180fda57</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>70c42ccbfd5ff509f9dea590</t>
@@ -1529,7 +1601,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1573,10 +1649,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -2023,13 +2111,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2082,7 +2174,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>4c5a44f13e0e4d538eb312b06d954e81</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>a9b768e8e21ab5f4fc183796</t>
@@ -2107,7 +2203,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2153,8 +2253,16 @@
       <c r="BH8" s="2" t="inlineStr"/>
       <c r="BI8" s="2" t="inlineStr"/>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2205,13 +2313,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2264,7 +2376,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>4ec19c7e11e541cf844a3809298f1b58</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>ecc1f87ddc7ddef11fcca85d</t>
@@ -2289,7 +2405,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -2335,8 +2455,16 @@
       <c r="BH9" s="2" t="inlineStr"/>
       <c r="BI9" s="2" t="inlineStr"/>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2387,13 +2515,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2446,7 +2578,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>1c6da8fcb9754126bb111294a5762fbe</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>b59739ae543c2c5e5b3b5a0c</t>
@@ -2471,7 +2607,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -2509,8 +2649,16 @@
       <c r="BH10" s="2" t="inlineStr"/>
       <c r="BI10" s="2" t="inlineStr"/>
       <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2561,13 +2709,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2620,7 +2772,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>11755b76fb8240b59518072254f4af74</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>40c55f9ba5806d258eee1041</t>
@@ -2645,7 +2801,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2691,8 +2851,16 @@
       <c r="BH11" s="2" t="inlineStr"/>
       <c r="BI11" s="2" t="inlineStr"/>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3697,13 +3865,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3756,7 +3928,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>c6a034619ec94069885cd044c46e330c</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>16a647aa9f85315de36625dd</t>
@@ -3781,7 +3957,11 @@
       <c r="AL17" s="2" t="inlineStr"/>
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr"/>
-      <c r="AO17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="2" t="inlineStr"/>
       <c r="AQ17" s="2" t="inlineStr"/>
       <c r="AR17" s="2" t="inlineStr"/>
@@ -3827,8 +4007,16 @@
       <c r="BH17" s="2" t="inlineStr"/>
       <c r="BI17" s="2" t="inlineStr"/>
       <c r="BJ17" s="2" t="inlineStr"/>
-      <c r="BK17" s="2" t="inlineStr"/>
-      <c r="BL17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">

--- a/news_daily/2026-10-07.xlsx
+++ b/news_daily/2026-10-07.xlsx
@@ -2894,10 +2894,14 @@
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>一般公司更新</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2910,7 +2914,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -2953,7 +2961,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -2966,7 +2974,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>5b28fde498e843ca991a5b1454878e6d</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>c06316e8e6c279e9b623ca95</t>
@@ -2991,7 +3003,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -3015,10 +3031,22 @@
       <c r="BF12" s="2" t="inlineStr"/>
       <c r="BG12" s="2" t="inlineStr"/>
       <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
